--- a/public/artifacts/reference-run/acme_security_questionnaire__DELIVERED.xlsx
+++ b/public/artifacts/reference-run/acme_security_questionnaire__DELIVERED.xlsx
@@ -532,7 +532,7 @@
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Evidence: POL-ISMS-001 v3.2 (para:2)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Evidence: POL-ISMS-001 v3.2 (para:3)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Evidence: CRT-SOC2-2025 v1.0 (para:2)
-[coverage=complete risk=medium human_review=yes]</t>
+[status=REQUIRES HUMAN coverage=complete risk=medium human_review=yes]</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
         <is>
           <t>Gaps: Retrieval found no sufficiently relevant approved evidence. | No approved evidence retrieved for this question.
 Routed: SME
-[coverage=none risk=medium human_review=yes]</t>
+[status=NO EVIDENCE coverage=none risk=medium human_review=yes]</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
         <is>
           <t>Gaps: RPT-PEN-2024 v1.0: EXPIRED 2025-06-10 — cannot support a current-state claim; route to security@acme.example
 Routed: SME
-[coverage=none risk=medium human_review=yes]</t>
+[status=NO EVIDENCE coverage=none risk=medium human_review=yes]</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Evidence: POL-SDLC-001 v1.2 (para:2)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Evidence: POL-AC-001 v2.3 (para:2)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Evidence: POL-AC-001 v2.3 (para:3)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
         <is>
           <t>Evidence: STD-ENC-001 v1.4 (para:2)
 Gaps: POL-RET-002 v1.1: EXPIRED 2026-06-20 — cannot support a current-state claim; route to infra@acme.example
-[coverage=partial risk=medium human_review=yes]</t>
+[status=PARTIAL coverage=partial risk=medium human_review=yes]</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         <is>
           <t>Evidence: STD-ENC-001 v1.4 (para:2)
 Gaps: POL-RET-002 v1.1: EXPIRED 2026-06-20 — cannot support a current-state claim; route to infra@acme.example
-[coverage=partial risk=medium human_review=yes]</t>
+[status=PARTIAL coverage=partial risk=medium human_review=yes]</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         <is>
           <t>Gaps: POL-RET-001: conflicting approved sources on a machine-checked assertion — route to owners for reconciliation | POL-RET-002 v1.1: EXPIRED 2026-06-20 — cannot support a current-state claim; route to infra@acme.example
 Routed: SOURCE_OWNER:infra@acme.example,privacy@acme.example
-[coverage=none risk=medium human_review=yes]</t>
+[status=NO EVIDENCE coverage=none risk=medium human_review=yes]</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Evidence: LST-SUBPROC-001 v4.0 (para:3)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
         <is>
           <t>Gaps: POL-RET-002 v1.1: EXPIRED 2026-06-20 — cannot support a current-state claim; route to infra@acme.example
 Routed: SME
-[coverage=none risk=medium human_review=yes]</t>
+[status=NO EVIDENCE coverage=none risk=medium human_review=yes]</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Evidence: POL-ISMS-001 v3.2 (para:4)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Evidence: PLN-IR-001 v2.1 (para:2)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Evidence: PLN-IR-001 v2.1 (para:3); PLN-BCP-001 v1.8 (para:3)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Evidence: PLN-BCP-001 v1.8 (para:2)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Evidence: POL-HR-001 v1.0 (para:2)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Evidence: POL-HR-001 v1.0 (para:3)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Evidence: POL-SDLC-001 v1.2 (para:2)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Evidence: POL-ISMS-001 v3.2 (para:5); STD-ENC-001 v1.4 (para:3)
-[coverage=complete risk=medium human_review=approved]</t>
+[status=EVIDENCE BACKED coverage=complete risk=medium human_review=approved]</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
         <is>
           <t>Gaps: Retrieval found no sufficiently relevant approved evidence. | No approved evidence retrieved for this question.
 Routed: SME
-[coverage=none risk=medium human_review=yes]</t>
+[status=NO EVIDENCE coverage=none risk=medium human_review=yes]</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
         <is>
           <t>Gaps: Question requests a contractual/legal commitment; outside answerable scope.
 Routed: LEGAL
-[coverage=none risk=high human_review=yes]</t>
+[status=ROUTED coverage=none risk=high human_review=yes]</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
         <is>
           <t>Gaps: POL-RET-001: conflicting approved sources on a machine-checked assertion — route to owners for reconciliation
 Routed: SOURCE_OWNER:infra@acme.example,privacy@acme.example
-[coverage=none risk=medium human_review=yes]</t>
+[status=NO EVIDENCE coverage=none risk=medium human_review=yes]</t>
         </is>
       </c>
     </row>
